--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/ESPELHO FREIO - 29_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/ESPELHO FREIO - 29_01.xlsx
@@ -492,7 +492,11 @@
       <c r="A4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>618341651142</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>ESPELHO FREIO DIANTEIRO IRON NXR125 025521</t>
@@ -657,45 +661,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>751320395689</t>
+          <t> </t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FLANGE TAMBOR FREIO TRASEIRO FABRECK CG FAN TITAN150/ START160</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -708,7 +704,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
@@ -721,7 +717,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/ESPELHO FREIO - 29_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/ESPELHO FREIO - 29_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -532,11 +512,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -557,11 +532,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -582,11 +552,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +572,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -632,11 +592,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,76 +612,214 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>12</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>15</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>17</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>25</v>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
         <v>31</v>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
